--- a/artfynd/A 14644-2024 artfynd.xlsx
+++ b/artfynd/A 14644-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY32"/>
+  <dimension ref="A1:AY45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4046,6 +4046,1384 @@
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>122745523</v>
+      </c>
+      <c r="B33" t="n">
+        <v>91186</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>2062</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Ulltickeporing</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Skeletocutis brevispora</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Nordanbro SV, Vb</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>776680</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7161613</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Elin Kollberg</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>122745524</v>
+      </c>
+      <c r="B34" t="n">
+        <v>90837</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Nordanbro S, Vb</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>776679</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7161610</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Elin Kollberg</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>122745519</v>
+      </c>
+      <c r="B35" t="n">
+        <v>98244</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Nordanbro SV, Vb</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>776678</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7161562</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Elin Kollberg</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>122745526</v>
+      </c>
+      <c r="B36" t="n">
+        <v>82447</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Nordanbro S, Vb</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>776671</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7161617</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Elin Kollberg</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>122745522</v>
+      </c>
+      <c r="B37" t="n">
+        <v>98244</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Nordanbro SV, Vb</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>776680</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7161612</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Elin Kollberg</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>122745527</v>
+      </c>
+      <c r="B38" t="n">
+        <v>74761</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Nordanbro S, Vb</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>776667</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7161621</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Elin Kollberg</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>122745525</v>
+      </c>
+      <c r="B39" t="n">
+        <v>91128</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>658</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Nordanbro S, Vb</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>776679</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7161607</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Elin Kollberg</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>122745520</v>
+      </c>
+      <c r="B40" t="n">
+        <v>92118</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Nordanbro SV, Vb</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>776684</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7161591</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Elin Kollberg</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>122745515</v>
+      </c>
+      <c r="B41" t="n">
+        <v>90851</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Nordanbro SV, Vb</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>776765</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7161494</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Elin Kollberg</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>122745516</v>
+      </c>
+      <c r="B42" t="n">
+        <v>98244</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Nordanbro SV, Vb</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>776687</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7161511</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Elin Kollberg</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>122745518</v>
+      </c>
+      <c r="B43" t="n">
+        <v>78694</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>185</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Nordanbro SV, Vb</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>776674</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7161575</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Elin Kollberg</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>122745517</v>
+      </c>
+      <c r="B44" t="n">
+        <v>90837</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Nordanbro SV, Vb</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>776700</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7161533</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Elin Kollberg</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>122745521</v>
+      </c>
+      <c r="B45" t="n">
+        <v>98244</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Nordanbro SV, Vb</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>776691</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7161596</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Elin Kollberg</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 14644-2024 artfynd.xlsx
+++ b/artfynd/A 14644-2024 artfynd.xlsx
@@ -4048,10 +4048,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122745523</v>
+        <v>122745517</v>
       </c>
       <c r="B33" t="n">
-        <v>91186</v>
+        <v>90940</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4060,25 +4060,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2062</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4088,10 +4088,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>776680</v>
+        <v>776700</v>
       </c>
       <c r="R33" t="n">
-        <v>7161613</v>
+        <v>7161533</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4154,10 +4154,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122745524</v>
+        <v>122745523</v>
       </c>
       <c r="B34" t="n">
-        <v>90837</v>
+        <v>91289</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4166,38 +4166,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>2062</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Nordanbro S, Vb</t>
+          <t>Nordanbro SV, Vb</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>776679</v>
+        <v>776680</v>
       </c>
       <c r="R34" t="n">
-        <v>7161610</v>
+        <v>7161613</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4260,10 +4260,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122745519</v>
+        <v>122745522</v>
       </c>
       <c r="B35" t="n">
-        <v>98244</v>
+        <v>98347</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4300,10 +4300,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>776678</v>
+        <v>776680</v>
       </c>
       <c r="R35" t="n">
-        <v>7161562</v>
+        <v>7161612</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4366,10 +4366,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122745526</v>
+        <v>122745518</v>
       </c>
       <c r="B36" t="n">
-        <v>82447</v>
+        <v>78796</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4382,34 +4382,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1312</v>
+        <v>185</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Nordanbro S, Vb</t>
+          <t>Nordanbro SV, Vb</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>776671</v>
+        <v>776674</v>
       </c>
       <c r="R36" t="n">
-        <v>7161617</v>
+        <v>7161575</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4472,10 +4472,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122745522</v>
+        <v>122745525</v>
       </c>
       <c r="B37" t="n">
-        <v>98244</v>
+        <v>91231</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4484,38 +4484,38 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Nordanbro SV, Vb</t>
+          <t>Nordanbro S, Vb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>776680</v>
+        <v>776679</v>
       </c>
       <c r="R37" t="n">
-        <v>7161612</v>
+        <v>7161607</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4578,10 +4578,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122745527</v>
+        <v>122745520</v>
       </c>
       <c r="B38" t="n">
-        <v>74761</v>
+        <v>92221</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4590,38 +4590,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6440</v>
+        <v>4364</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Nordanbro S, Vb</t>
+          <t>Nordanbro SV, Vb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>776667</v>
+        <v>776684</v>
       </c>
       <c r="R38" t="n">
-        <v>7161621</v>
+        <v>7161591</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4684,10 +4684,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122745525</v>
+        <v>122745515</v>
       </c>
       <c r="B39" t="n">
-        <v>91128</v>
+        <v>90954</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4700,34 +4700,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>658</v>
+        <v>1204</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Nordanbro S, Vb</t>
+          <t>Nordanbro SV, Vb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>776679</v>
+        <v>776765</v>
       </c>
       <c r="R39" t="n">
-        <v>7161607</v>
+        <v>7161494</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4790,10 +4790,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122745520</v>
+        <v>122745526</v>
       </c>
       <c r="B40" t="n">
-        <v>92118</v>
+        <v>82549</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4802,38 +4802,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4364</v>
+        <v>1312</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Nordanbro SV, Vb</t>
+          <t>Nordanbro S, Vb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>776684</v>
+        <v>776671</v>
       </c>
       <c r="R40" t="n">
-        <v>7161591</v>
+        <v>7161617</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4896,10 +4896,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122745515</v>
+        <v>122745516</v>
       </c>
       <c r="B41" t="n">
-        <v>90851</v>
+        <v>98347</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4908,25 +4908,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1204</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4936,10 +4936,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>776765</v>
+        <v>776687</v>
       </c>
       <c r="R41" t="n">
-        <v>7161494</v>
+        <v>7161511</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5002,10 +5002,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122745516</v>
+        <v>122745527</v>
       </c>
       <c r="B42" t="n">
-        <v>98244</v>
+        <v>74863</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5014,38 +5014,38 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Nordanbro SV, Vb</t>
+          <t>Nordanbro S, Vb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>776687</v>
+        <v>776667</v>
       </c>
       <c r="R42" t="n">
-        <v>7161511</v>
+        <v>7161621</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5108,10 +5108,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122745518</v>
+        <v>122745521</v>
       </c>
       <c r="B43" t="n">
-        <v>78694</v>
+        <v>98347</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5120,25 +5120,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5148,10 +5148,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>776674</v>
+        <v>776691</v>
       </c>
       <c r="R43" t="n">
-        <v>7161575</v>
+        <v>7161596</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5214,10 +5214,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122745517</v>
+        <v>122745524</v>
       </c>
       <c r="B44" t="n">
-        <v>90837</v>
+        <v>90940</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5250,14 +5250,14 @@
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Nordanbro SV, Vb</t>
+          <t>Nordanbro S, Vb</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>776700</v>
+        <v>776679</v>
       </c>
       <c r="R44" t="n">
-        <v>7161533</v>
+        <v>7161610</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5320,10 +5320,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122745521</v>
+        <v>122745519</v>
       </c>
       <c r="B45" t="n">
-        <v>98244</v>
+        <v>98347</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5360,10 +5360,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>776691</v>
+        <v>776678</v>
       </c>
       <c r="R45" t="n">
-        <v>7161596</v>
+        <v>7161562</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>

--- a/artfynd/A 14644-2024 artfynd.xlsx
+++ b/artfynd/A 14644-2024 artfynd.xlsx
@@ -4790,10 +4790,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122745526</v>
+        <v>122745516</v>
       </c>
       <c r="B40" t="n">
-        <v>82549</v>
+        <v>98347</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4802,38 +4802,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Nordanbro S, Vb</t>
+          <t>Nordanbro SV, Vb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>776671</v>
+        <v>776687</v>
       </c>
       <c r="R40" t="n">
-        <v>7161617</v>
+        <v>7161511</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4896,10 +4896,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122745516</v>
+        <v>122745526</v>
       </c>
       <c r="B41" t="n">
-        <v>98347</v>
+        <v>82549</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4908,38 +4908,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Nordanbro SV, Vb</t>
+          <t>Nordanbro S, Vb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>776687</v>
+        <v>776671</v>
       </c>
       <c r="R41" t="n">
-        <v>7161511</v>
+        <v>7161617</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5214,10 +5214,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122745524</v>
+        <v>122745519</v>
       </c>
       <c r="B44" t="n">
-        <v>90940</v>
+        <v>98347</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5226,38 +5226,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Nordanbro S, Vb</t>
+          <t>Nordanbro SV, Vb</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>776679</v>
+        <v>776678</v>
       </c>
       <c r="R44" t="n">
-        <v>7161610</v>
+        <v>7161562</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5320,10 +5320,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122745519</v>
+        <v>122745524</v>
       </c>
       <c r="B45" t="n">
-        <v>98347</v>
+        <v>90940</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5332,38 +5332,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Nordanbro SV, Vb</t>
+          <t>Nordanbro S, Vb</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>776678</v>
+        <v>776679</v>
       </c>
       <c r="R45" t="n">
-        <v>7161562</v>
+        <v>7161610</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>

--- a/artfynd/A 14644-2024 artfynd.xlsx
+++ b/artfynd/A 14644-2024 artfynd.xlsx
@@ -4048,10 +4048,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122745517</v>
+        <v>122745520</v>
       </c>
       <c r="B33" t="n">
-        <v>90940</v>
+        <v>92225</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4060,25 +4060,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4088,10 +4088,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>776700</v>
+        <v>776684</v>
       </c>
       <c r="R33" t="n">
-        <v>7161533</v>
+        <v>7161591</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4154,10 +4154,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122745523</v>
+        <v>122745521</v>
       </c>
       <c r="B34" t="n">
-        <v>91289</v>
+        <v>98355</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4170,21 +4170,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2062</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4194,10 +4194,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>776680</v>
+        <v>776691</v>
       </c>
       <c r="R34" t="n">
-        <v>7161613</v>
+        <v>7161596</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4260,10 +4260,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122745522</v>
+        <v>122745525</v>
       </c>
       <c r="B35" t="n">
-        <v>98347</v>
+        <v>91235</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4272,38 +4272,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Nordanbro SV, Vb</t>
+          <t>Nordanbro S, Vb</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>776680</v>
+        <v>776679</v>
       </c>
       <c r="R35" t="n">
-        <v>7161612</v>
+        <v>7161607</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4366,10 +4366,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122745518</v>
+        <v>122745523</v>
       </c>
       <c r="B36" t="n">
-        <v>78796</v>
+        <v>91293</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4378,25 +4378,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>185</v>
+        <v>2062</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4406,10 +4406,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>776674</v>
+        <v>776680</v>
       </c>
       <c r="R36" t="n">
-        <v>7161575</v>
+        <v>7161613</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4472,10 +4472,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122745525</v>
+        <v>122745516</v>
       </c>
       <c r="B37" t="n">
-        <v>91231</v>
+        <v>98355</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4484,38 +4484,38 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Nordanbro S, Vb</t>
+          <t>Nordanbro SV, Vb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>776679</v>
+        <v>776687</v>
       </c>
       <c r="R37" t="n">
-        <v>7161607</v>
+        <v>7161511</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4578,10 +4578,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122745520</v>
+        <v>122745524</v>
       </c>
       <c r="B38" t="n">
-        <v>92221</v>
+        <v>90944</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4590,38 +4590,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Nordanbro SV, Vb</t>
+          <t>Nordanbro S, Vb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>776684</v>
+        <v>776679</v>
       </c>
       <c r="R38" t="n">
-        <v>7161591</v>
+        <v>7161610</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4684,10 +4684,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122745515</v>
+        <v>122745517</v>
       </c>
       <c r="B39" t="n">
-        <v>90954</v>
+        <v>90944</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4700,21 +4700,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4724,10 +4724,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>776765</v>
+        <v>776700</v>
       </c>
       <c r="R39" t="n">
-        <v>7161494</v>
+        <v>7161533</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4790,10 +4790,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122745516</v>
+        <v>122745527</v>
       </c>
       <c r="B40" t="n">
-        <v>98347</v>
+        <v>74863</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4802,38 +4802,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Nordanbro SV, Vb</t>
+          <t>Nordanbro S, Vb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>776687</v>
+        <v>776667</v>
       </c>
       <c r="R40" t="n">
-        <v>7161511</v>
+        <v>7161621</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4896,10 +4896,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122745526</v>
+        <v>122745519</v>
       </c>
       <c r="B41" t="n">
-        <v>82549</v>
+        <v>98355</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4908,38 +4908,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Nordanbro S, Vb</t>
+          <t>Nordanbro SV, Vb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>776671</v>
+        <v>776678</v>
       </c>
       <c r="R41" t="n">
-        <v>7161617</v>
+        <v>7161562</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5002,10 +5002,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122745527</v>
+        <v>122745515</v>
       </c>
       <c r="B42" t="n">
-        <v>74863</v>
+        <v>90958</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5018,34 +5018,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6440</v>
+        <v>1204</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Nordanbro S, Vb</t>
+          <t>Nordanbro SV, Vb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>776667</v>
+        <v>776765</v>
       </c>
       <c r="R42" t="n">
-        <v>7161621</v>
+        <v>7161494</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5108,10 +5108,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122745521</v>
+        <v>122745518</v>
       </c>
       <c r="B43" t="n">
-        <v>98347</v>
+        <v>78800</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5120,25 +5120,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5148,10 +5148,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>776691</v>
+        <v>776674</v>
       </c>
       <c r="R43" t="n">
-        <v>7161596</v>
+        <v>7161575</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5214,10 +5214,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122745519</v>
+        <v>122745526</v>
       </c>
       <c r="B44" t="n">
-        <v>98347</v>
+        <v>82553</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5226,38 +5226,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Nordanbro SV, Vb</t>
+          <t>Nordanbro S, Vb</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>776678</v>
+        <v>776671</v>
       </c>
       <c r="R44" t="n">
-        <v>7161562</v>
+        <v>7161617</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5320,10 +5320,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122745524</v>
+        <v>122745522</v>
       </c>
       <c r="B45" t="n">
-        <v>90940</v>
+        <v>98355</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5332,38 +5332,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Nordanbro S, Vb</t>
+          <t>Nordanbro SV, Vb</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>776679</v>
+        <v>776680</v>
       </c>
       <c r="R45" t="n">
-        <v>7161610</v>
+        <v>7161612</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>

--- a/artfynd/A 14644-2024 artfynd.xlsx
+++ b/artfynd/A 14644-2024 artfynd.xlsx
@@ -4790,10 +4790,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122745527</v>
+        <v>122745515</v>
       </c>
       <c r="B40" t="n">
-        <v>74863</v>
+        <v>90958</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4806,34 +4806,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6440</v>
+        <v>1204</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Nordanbro S, Vb</t>
+          <t>Nordanbro SV, Vb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>776667</v>
+        <v>776765</v>
       </c>
       <c r="R40" t="n">
-        <v>7161621</v>
+        <v>7161494</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4896,10 +4896,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122745519</v>
+        <v>122745527</v>
       </c>
       <c r="B41" t="n">
-        <v>98355</v>
+        <v>74863</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4908,38 +4908,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Nordanbro SV, Vb</t>
+          <t>Nordanbro S, Vb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>776678</v>
+        <v>776667</v>
       </c>
       <c r="R41" t="n">
-        <v>7161562</v>
+        <v>7161621</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5002,10 +5002,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122745515</v>
+        <v>122745519</v>
       </c>
       <c r="B42" t="n">
-        <v>90958</v>
+        <v>98355</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5014,25 +5014,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1204</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5042,10 +5042,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>776765</v>
+        <v>776678</v>
       </c>
       <c r="R42" t="n">
-        <v>7161494</v>
+        <v>7161562</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>

--- a/artfynd/A 14644-2024 artfynd.xlsx
+++ b/artfynd/A 14644-2024 artfynd.xlsx
@@ -4048,10 +4048,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122745520</v>
+        <v>122745526</v>
       </c>
       <c r="B33" t="n">
-        <v>92225</v>
+        <v>82553</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4060,38 +4060,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4364</v>
+        <v>1312</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Nordanbro SV, Vb</t>
+          <t>Nordanbro S, Vb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>776684</v>
+        <v>776671</v>
       </c>
       <c r="R33" t="n">
-        <v>7161591</v>
+        <v>7161617</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4154,10 +4154,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122745521</v>
+        <v>122745523</v>
       </c>
       <c r="B34" t="n">
-        <v>98355</v>
+        <v>91293</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4170,21 +4170,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>2062</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4194,10 +4194,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>776691</v>
+        <v>776680</v>
       </c>
       <c r="R34" t="n">
-        <v>7161596</v>
+        <v>7161613</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4260,10 +4260,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122745525</v>
+        <v>122745524</v>
       </c>
       <c r="B35" t="n">
-        <v>91235</v>
+        <v>90944</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4276,21 +4276,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4303,7 +4303,7 @@
         <v>776679</v>
       </c>
       <c r="R35" t="n">
-        <v>7161607</v>
+        <v>7161610</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4366,10 +4366,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122745523</v>
+        <v>122745525</v>
       </c>
       <c r="B36" t="n">
-        <v>91293</v>
+        <v>91235</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4378,38 +4378,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2062</v>
+        <v>658</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Nordanbro SV, Vb</t>
+          <t>Nordanbro S, Vb</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>776680</v>
+        <v>776679</v>
       </c>
       <c r="R36" t="n">
-        <v>7161613</v>
+        <v>7161607</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4472,10 +4472,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122745516</v>
+        <v>122745517</v>
       </c>
       <c r="B37" t="n">
-        <v>98355</v>
+        <v>90944</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4484,25 +4484,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4512,10 +4512,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>776687</v>
+        <v>776700</v>
       </c>
       <c r="R37" t="n">
-        <v>7161511</v>
+        <v>7161533</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4578,10 +4578,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122745524</v>
+        <v>122745518</v>
       </c>
       <c r="B38" t="n">
-        <v>90944</v>
+        <v>78800</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4594,34 +4594,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>185</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Nordanbro S, Vb</t>
+          <t>Nordanbro SV, Vb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>776679</v>
+        <v>776674</v>
       </c>
       <c r="R38" t="n">
-        <v>7161610</v>
+        <v>7161575</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4684,10 +4684,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122745517</v>
+        <v>122745522</v>
       </c>
       <c r="B39" t="n">
-        <v>90944</v>
+        <v>98355</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4696,25 +4696,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4724,10 +4724,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>776700</v>
+        <v>776680</v>
       </c>
       <c r="R39" t="n">
-        <v>7161533</v>
+        <v>7161612</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4790,10 +4790,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122745515</v>
+        <v>122745520</v>
       </c>
       <c r="B40" t="n">
-        <v>90958</v>
+        <v>92225</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4802,25 +4802,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1204</v>
+        <v>4364</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4830,10 +4830,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>776765</v>
+        <v>776684</v>
       </c>
       <c r="R40" t="n">
-        <v>7161494</v>
+        <v>7161591</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4896,10 +4896,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122745527</v>
+        <v>122745515</v>
       </c>
       <c r="B41" t="n">
-        <v>74863</v>
+        <v>90958</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4912,34 +4912,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6440</v>
+        <v>1204</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Nordanbro S, Vb</t>
+          <t>Nordanbro SV, Vb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>776667</v>
+        <v>776765</v>
       </c>
       <c r="R41" t="n">
-        <v>7161621</v>
+        <v>7161494</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5108,10 +5108,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122745518</v>
+        <v>122745521</v>
       </c>
       <c r="B43" t="n">
-        <v>78800</v>
+        <v>98355</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5120,25 +5120,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5148,10 +5148,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>776674</v>
+        <v>776691</v>
       </c>
       <c r="R43" t="n">
-        <v>7161575</v>
+        <v>7161596</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5214,10 +5214,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122745526</v>
+        <v>122745516</v>
       </c>
       <c r="B44" t="n">
-        <v>82553</v>
+        <v>98355</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5226,38 +5226,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Nordanbro S, Vb</t>
+          <t>Nordanbro SV, Vb</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>776671</v>
+        <v>776687</v>
       </c>
       <c r="R44" t="n">
-        <v>7161617</v>
+        <v>7161511</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5320,10 +5320,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122745522</v>
+        <v>122745527</v>
       </c>
       <c r="B45" t="n">
-        <v>98355</v>
+        <v>74863</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5332,38 +5332,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Nordanbro SV, Vb</t>
+          <t>Nordanbro S, Vb</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>776680</v>
+        <v>776667</v>
       </c>
       <c r="R45" t="n">
-        <v>7161612</v>
+        <v>7161621</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>

--- a/artfynd/A 14644-2024 artfynd.xlsx
+++ b/artfynd/A 14644-2024 artfynd.xlsx
@@ -4048,10 +4048,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122745526</v>
+        <v>122745520</v>
       </c>
       <c r="B33" t="n">
-        <v>82553</v>
+        <v>92225</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4060,38 +4060,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1312</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Nordanbro S, Vb</t>
+          <t>Nordanbro SV, Vb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>776671</v>
+        <v>776684</v>
       </c>
       <c r="R33" t="n">
-        <v>7161617</v>
+        <v>7161591</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4154,10 +4154,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122745523</v>
+        <v>122745521</v>
       </c>
       <c r="B34" t="n">
-        <v>91293</v>
+        <v>98357</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4170,21 +4170,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2062</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4194,10 +4194,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>776680</v>
+        <v>776691</v>
       </c>
       <c r="R34" t="n">
-        <v>7161613</v>
+        <v>7161596</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4260,7 +4260,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122745524</v>
+        <v>122745517</v>
       </c>
       <c r="B35" t="n">
         <v>90944</v>
@@ -4296,14 +4296,14 @@
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Nordanbro S, Vb</t>
+          <t>Nordanbro SV, Vb</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>776679</v>
+        <v>776700</v>
       </c>
       <c r="R35" t="n">
-        <v>7161610</v>
+        <v>7161533</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4366,10 +4366,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122745525</v>
+        <v>122745516</v>
       </c>
       <c r="B36" t="n">
-        <v>91235</v>
+        <v>98357</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4378,38 +4378,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Nordanbro S, Vb</t>
+          <t>Nordanbro SV, Vb</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>776679</v>
+        <v>776687</v>
       </c>
       <c r="R36" t="n">
-        <v>7161607</v>
+        <v>7161511</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4472,10 +4472,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122745517</v>
+        <v>122745519</v>
       </c>
       <c r="B37" t="n">
-        <v>90944</v>
+        <v>98357</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4484,25 +4484,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4512,10 +4512,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>776700</v>
+        <v>776678</v>
       </c>
       <c r="R37" t="n">
-        <v>7161533</v>
+        <v>7161562</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4578,10 +4578,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122745518</v>
+        <v>122745524</v>
       </c>
       <c r="B38" t="n">
-        <v>78800</v>
+        <v>90944</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4594,34 +4594,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>185</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Nordanbro SV, Vb</t>
+          <t>Nordanbro S, Vb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>776674</v>
+        <v>776679</v>
       </c>
       <c r="R38" t="n">
-        <v>7161575</v>
+        <v>7161610</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4684,10 +4684,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122745522</v>
+        <v>122745525</v>
       </c>
       <c r="B39" t="n">
-        <v>98355</v>
+        <v>91235</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4696,38 +4696,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Nordanbro SV, Vb</t>
+          <t>Nordanbro S, Vb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>776680</v>
+        <v>776679</v>
       </c>
       <c r="R39" t="n">
-        <v>7161612</v>
+        <v>7161607</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4790,10 +4790,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122745520</v>
+        <v>122745526</v>
       </c>
       <c r="B40" t="n">
-        <v>92225</v>
+        <v>82553</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4802,38 +4802,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4364</v>
+        <v>1312</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Nordanbro SV, Vb</t>
+          <t>Nordanbro S, Vb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>776684</v>
+        <v>776671</v>
       </c>
       <c r="R40" t="n">
-        <v>7161591</v>
+        <v>7161617</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4896,10 +4896,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122745515</v>
+        <v>122745523</v>
       </c>
       <c r="B41" t="n">
-        <v>90958</v>
+        <v>91293</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4908,25 +4908,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1204</v>
+        <v>2062</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4936,10 +4936,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>776765</v>
+        <v>776680</v>
       </c>
       <c r="R41" t="n">
-        <v>7161494</v>
+        <v>7161613</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5002,10 +5002,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122745519</v>
+        <v>122745522</v>
       </c>
       <c r="B42" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5042,10 +5042,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>776678</v>
+        <v>776680</v>
       </c>
       <c r="R42" t="n">
-        <v>7161562</v>
+        <v>7161612</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5108,10 +5108,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122745521</v>
+        <v>122745518</v>
       </c>
       <c r="B43" t="n">
-        <v>98355</v>
+        <v>78800</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5120,25 +5120,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5148,10 +5148,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>776691</v>
+        <v>776674</v>
       </c>
       <c r="R43" t="n">
-        <v>7161596</v>
+        <v>7161575</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5214,10 +5214,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122745516</v>
+        <v>122745527</v>
       </c>
       <c r="B44" t="n">
-        <v>98355</v>
+        <v>74863</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5226,38 +5226,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Nordanbro SV, Vb</t>
+          <t>Nordanbro S, Vb</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>776687</v>
+        <v>776667</v>
       </c>
       <c r="R44" t="n">
-        <v>7161511</v>
+        <v>7161621</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5320,10 +5320,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122745527</v>
+        <v>122745515</v>
       </c>
       <c r="B45" t="n">
-        <v>74863</v>
+        <v>90958</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5336,34 +5336,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6440</v>
+        <v>1204</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Nordanbro S, Vb</t>
+          <t>Nordanbro SV, Vb</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>776667</v>
+        <v>776765</v>
       </c>
       <c r="R45" t="n">
-        <v>7161621</v>
+        <v>7161494</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>

--- a/artfynd/A 14644-2024 artfynd.xlsx
+++ b/artfynd/A 14644-2024 artfynd.xlsx
@@ -4048,10 +4048,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122745520</v>
+        <v>122745518</v>
       </c>
       <c r="B33" t="n">
-        <v>92225</v>
+        <v>78800</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4060,25 +4060,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4364</v>
+        <v>185</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4088,10 +4088,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>776684</v>
+        <v>776674</v>
       </c>
       <c r="R33" t="n">
-        <v>7161591</v>
+        <v>7161575</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4154,10 +4154,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122745521</v>
+        <v>122745523</v>
       </c>
       <c r="B34" t="n">
-        <v>98357</v>
+        <v>91293</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4170,21 +4170,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>2062</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4194,10 +4194,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>776691</v>
+        <v>776680</v>
       </c>
       <c r="R34" t="n">
-        <v>7161596</v>
+        <v>7161613</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4260,10 +4260,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122745517</v>
+        <v>122745519</v>
       </c>
       <c r="B35" t="n">
-        <v>90944</v>
+        <v>98357</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4272,25 +4272,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4300,10 +4300,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>776700</v>
+        <v>776678</v>
       </c>
       <c r="R35" t="n">
-        <v>7161533</v>
+        <v>7161562</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4366,7 +4366,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122745516</v>
+        <v>122745522</v>
       </c>
       <c r="B36" t="n">
         <v>98357</v>
@@ -4406,10 +4406,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>776687</v>
+        <v>776680</v>
       </c>
       <c r="R36" t="n">
-        <v>7161511</v>
+        <v>7161612</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4472,10 +4472,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122745519</v>
+        <v>122745517</v>
       </c>
       <c r="B37" t="n">
-        <v>98357</v>
+        <v>90944</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4484,25 +4484,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4512,10 +4512,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>776678</v>
+        <v>776700</v>
       </c>
       <c r="R37" t="n">
-        <v>7161562</v>
+        <v>7161533</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4578,10 +4578,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122745524</v>
+        <v>122745525</v>
       </c>
       <c r="B38" t="n">
-        <v>90944</v>
+        <v>91235</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4594,21 +4594,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4621,7 +4621,7 @@
         <v>776679</v>
       </c>
       <c r="R38" t="n">
-        <v>7161610</v>
+        <v>7161607</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4684,10 +4684,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122745525</v>
+        <v>122745526</v>
       </c>
       <c r="B39" t="n">
-        <v>91235</v>
+        <v>82553</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4700,21 +4700,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>658</v>
+        <v>1312</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4724,10 +4724,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>776679</v>
+        <v>776671</v>
       </c>
       <c r="R39" t="n">
-        <v>7161607</v>
+        <v>7161617</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4790,10 +4790,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122745526</v>
+        <v>122745515</v>
       </c>
       <c r="B40" t="n">
-        <v>82553</v>
+        <v>90958</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4806,34 +4806,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1312</v>
+        <v>1204</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Nordanbro S, Vb</t>
+          <t>Nordanbro SV, Vb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>776671</v>
+        <v>776765</v>
       </c>
       <c r="R40" t="n">
-        <v>7161617</v>
+        <v>7161494</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4896,10 +4896,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122745523</v>
+        <v>122745521</v>
       </c>
       <c r="B41" t="n">
-        <v>91293</v>
+        <v>98357</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4912,21 +4912,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2062</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4936,10 +4936,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>776680</v>
+        <v>776691</v>
       </c>
       <c r="R41" t="n">
-        <v>7161613</v>
+        <v>7161596</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5002,10 +5002,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122745522</v>
+        <v>122745520</v>
       </c>
       <c r="B42" t="n">
-        <v>98357</v>
+        <v>92225</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5014,25 +5014,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5042,10 +5042,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>776680</v>
+        <v>776684</v>
       </c>
       <c r="R42" t="n">
-        <v>7161612</v>
+        <v>7161591</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5108,10 +5108,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122745518</v>
+        <v>122745516</v>
       </c>
       <c r="B43" t="n">
-        <v>78800</v>
+        <v>98357</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5120,25 +5120,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5148,10 +5148,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>776674</v>
+        <v>776687</v>
       </c>
       <c r="R43" t="n">
-        <v>7161575</v>
+        <v>7161511</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5320,10 +5320,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122745515</v>
+        <v>122745524</v>
       </c>
       <c r="B45" t="n">
-        <v>90958</v>
+        <v>90944</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5336,34 +5336,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Nordanbro SV, Vb</t>
+          <t>Nordanbro S, Vb</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>776765</v>
+        <v>776679</v>
       </c>
       <c r="R45" t="n">
-        <v>7161494</v>
+        <v>7161610</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>

--- a/artfynd/A 14644-2024 artfynd.xlsx
+++ b/artfynd/A 14644-2024 artfynd.xlsx
@@ -4366,10 +4366,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122745522</v>
+        <v>122745517</v>
       </c>
       <c r="B36" t="n">
-        <v>98357</v>
+        <v>90944</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4378,25 +4378,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4406,10 +4406,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>776680</v>
+        <v>776700</v>
       </c>
       <c r="R36" t="n">
-        <v>7161612</v>
+        <v>7161533</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4472,10 +4472,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122745517</v>
+        <v>122745522</v>
       </c>
       <c r="B37" t="n">
-        <v>90944</v>
+        <v>98357</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4484,25 +4484,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4512,10 +4512,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>776700</v>
+        <v>776680</v>
       </c>
       <c r="R37" t="n">
-        <v>7161533</v>
+        <v>7161612</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>

--- a/artfynd/A 14644-2024 artfynd.xlsx
+++ b/artfynd/A 14644-2024 artfynd.xlsx
@@ -4048,10 +4048,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122745518</v>
+        <v>122745517</v>
       </c>
       <c r="B33" t="n">
-        <v>78800</v>
+        <v>90952</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4064,21 +4064,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>185</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4088,10 +4088,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>776674</v>
+        <v>776700</v>
       </c>
       <c r="R33" t="n">
-        <v>7161575</v>
+        <v>7161533</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4154,10 +4154,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122745523</v>
+        <v>122745527</v>
       </c>
       <c r="B34" t="n">
-        <v>91293</v>
+        <v>74863</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4166,38 +4166,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2062</v>
+        <v>6440</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Nordanbro SV, Vb</t>
+          <t>Nordanbro S, Vb</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>776680</v>
+        <v>776667</v>
       </c>
       <c r="R34" t="n">
-        <v>7161613</v>
+        <v>7161621</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4260,10 +4260,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122745519</v>
+        <v>122745524</v>
       </c>
       <c r="B35" t="n">
-        <v>98357</v>
+        <v>90952</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4272,38 +4272,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Nordanbro SV, Vb</t>
+          <t>Nordanbro S, Vb</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>776678</v>
+        <v>776679</v>
       </c>
       <c r="R35" t="n">
-        <v>7161562</v>
+        <v>7161610</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4366,10 +4366,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122745517</v>
+        <v>122745520</v>
       </c>
       <c r="B36" t="n">
-        <v>90944</v>
+        <v>92233</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4378,25 +4378,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4406,10 +4406,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>776700</v>
+        <v>776684</v>
       </c>
       <c r="R36" t="n">
-        <v>7161533</v>
+        <v>7161591</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4472,10 +4472,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122745522</v>
+        <v>122745518</v>
       </c>
       <c r="B37" t="n">
-        <v>98357</v>
+        <v>78800</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4484,25 +4484,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4512,10 +4512,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>776680</v>
+        <v>776674</v>
       </c>
       <c r="R37" t="n">
-        <v>7161612</v>
+        <v>7161575</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4578,10 +4578,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122745525</v>
+        <v>122745516</v>
       </c>
       <c r="B38" t="n">
-        <v>91235</v>
+        <v>98365</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4590,38 +4590,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Nordanbro S, Vb</t>
+          <t>Nordanbro SV, Vb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>776679</v>
+        <v>776687</v>
       </c>
       <c r="R38" t="n">
-        <v>7161607</v>
+        <v>7161511</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4684,10 +4684,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122745526</v>
+        <v>122745521</v>
       </c>
       <c r="B39" t="n">
-        <v>82553</v>
+        <v>98365</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4696,38 +4696,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Nordanbro S, Vb</t>
+          <t>Nordanbro SV, Vb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>776671</v>
+        <v>776691</v>
       </c>
       <c r="R39" t="n">
-        <v>7161617</v>
+        <v>7161596</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4790,10 +4790,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122745515</v>
+        <v>122745523</v>
       </c>
       <c r="B40" t="n">
-        <v>90958</v>
+        <v>91301</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4802,25 +4802,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1204</v>
+        <v>2062</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4830,10 +4830,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>776765</v>
+        <v>776680</v>
       </c>
       <c r="R40" t="n">
-        <v>7161494</v>
+        <v>7161613</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4896,10 +4896,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122745521</v>
+        <v>122745525</v>
       </c>
       <c r="B41" t="n">
-        <v>98357</v>
+        <v>91243</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4908,38 +4908,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Nordanbro SV, Vb</t>
+          <t>Nordanbro S, Vb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>776691</v>
+        <v>776679</v>
       </c>
       <c r="R41" t="n">
-        <v>7161596</v>
+        <v>7161607</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5002,10 +5002,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122745520</v>
+        <v>122745515</v>
       </c>
       <c r="B42" t="n">
-        <v>92225</v>
+        <v>90966</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5014,25 +5014,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4364</v>
+        <v>1204</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5042,10 +5042,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>776684</v>
+        <v>776765</v>
       </c>
       <c r="R42" t="n">
-        <v>7161591</v>
+        <v>7161494</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5108,10 +5108,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122745516</v>
+        <v>122745519</v>
       </c>
       <c r="B43" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5148,10 +5148,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>776687</v>
+        <v>776678</v>
       </c>
       <c r="R43" t="n">
-        <v>7161511</v>
+        <v>7161562</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5214,10 +5214,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122745527</v>
+        <v>122745522</v>
       </c>
       <c r="B44" t="n">
-        <v>74863</v>
+        <v>98365</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5226,38 +5226,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Nordanbro S, Vb</t>
+          <t>Nordanbro SV, Vb</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>776667</v>
+        <v>776680</v>
       </c>
       <c r="R44" t="n">
-        <v>7161621</v>
+        <v>7161612</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5320,10 +5320,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122745524</v>
+        <v>122745526</v>
       </c>
       <c r="B45" t="n">
-        <v>90944</v>
+        <v>82553</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5336,21 +5336,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5360,10 +5360,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>776679</v>
+        <v>776671</v>
       </c>
       <c r="R45" t="n">
-        <v>7161610</v>
+        <v>7161617</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>

--- a/artfynd/A 14644-2024 artfynd.xlsx
+++ b/artfynd/A 14644-2024 artfynd.xlsx
@@ -4048,10 +4048,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122745517</v>
+        <v>122745527</v>
       </c>
       <c r="B33" t="n">
-        <v>90952</v>
+        <v>74863</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4064,34 +4064,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Nordanbro SV, Vb</t>
+          <t>Nordanbro S, Vb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>776700</v>
+        <v>776667</v>
       </c>
       <c r="R33" t="n">
-        <v>7161533</v>
+        <v>7161621</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4154,10 +4154,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122745527</v>
+        <v>122745517</v>
       </c>
       <c r="B34" t="n">
-        <v>74863</v>
+        <v>90952</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4170,34 +4170,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Nordanbro S, Vb</t>
+          <t>Nordanbro SV, Vb</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>776667</v>
+        <v>776700</v>
       </c>
       <c r="R34" t="n">
-        <v>7161621</v>
+        <v>7161533</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4578,7 +4578,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122745516</v>
+        <v>122745521</v>
       </c>
       <c r="B38" t="n">
         <v>98365</v>
@@ -4618,10 +4618,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>776687</v>
+        <v>776691</v>
       </c>
       <c r="R38" t="n">
-        <v>7161511</v>
+        <v>7161596</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4684,7 +4684,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122745521</v>
+        <v>122745516</v>
       </c>
       <c r="B39" t="n">
         <v>98365</v>
@@ -4724,10 +4724,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>776691</v>
+        <v>776687</v>
       </c>
       <c r="R39" t="n">
-        <v>7161596</v>
+        <v>7161511</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>

--- a/artfynd/A 14644-2024 artfynd.xlsx
+++ b/artfynd/A 14644-2024 artfynd.xlsx
@@ -4048,10 +4048,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122745527</v>
+        <v>122745520</v>
       </c>
       <c r="B33" t="n">
-        <v>74863</v>
+        <v>92233</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4060,38 +4060,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6440</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Nordanbro S, Vb</t>
+          <t>Nordanbro SV, Vb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>776667</v>
+        <v>776684</v>
       </c>
       <c r="R33" t="n">
-        <v>7161621</v>
+        <v>7161591</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4154,10 +4154,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122745517</v>
+        <v>122745521</v>
       </c>
       <c r="B34" t="n">
-        <v>90952</v>
+        <v>98365</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4166,25 +4166,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4194,10 +4194,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>776700</v>
+        <v>776691</v>
       </c>
       <c r="R34" t="n">
-        <v>7161533</v>
+        <v>7161596</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4260,10 +4260,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122745524</v>
+        <v>122745515</v>
       </c>
       <c r="B35" t="n">
-        <v>90952</v>
+        <v>90966</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4276,34 +4276,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Nordanbro S, Vb</t>
+          <t>Nordanbro SV, Vb</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>776679</v>
+        <v>776765</v>
       </c>
       <c r="R35" t="n">
-        <v>7161610</v>
+        <v>7161494</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4366,10 +4366,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122745520</v>
+        <v>122745526</v>
       </c>
       <c r="B36" t="n">
-        <v>92233</v>
+        <v>82553</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4378,38 +4378,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4364</v>
+        <v>1312</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Nordanbro SV, Vb</t>
+          <t>Nordanbro S, Vb</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>776684</v>
+        <v>776671</v>
       </c>
       <c r="R36" t="n">
-        <v>7161591</v>
+        <v>7161617</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4472,10 +4472,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122745518</v>
+        <v>122745525</v>
       </c>
       <c r="B37" t="n">
-        <v>78800</v>
+        <v>91243</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4488,34 +4488,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>185</v>
+        <v>658</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Nordanbro SV, Vb</t>
+          <t>Nordanbro S, Vb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>776674</v>
+        <v>776679</v>
       </c>
       <c r="R37" t="n">
-        <v>7161575</v>
+        <v>7161607</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4578,10 +4578,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122745521</v>
+        <v>122745523</v>
       </c>
       <c r="B38" t="n">
-        <v>98365</v>
+        <v>91301</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4594,21 +4594,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>2062</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4618,10 +4618,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>776691</v>
+        <v>776680</v>
       </c>
       <c r="R38" t="n">
-        <v>7161596</v>
+        <v>7161613</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4684,10 +4684,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122745516</v>
+        <v>122745524</v>
       </c>
       <c r="B39" t="n">
-        <v>98365</v>
+        <v>90952</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4696,38 +4696,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Nordanbro SV, Vb</t>
+          <t>Nordanbro S, Vb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>776687</v>
+        <v>776679</v>
       </c>
       <c r="R39" t="n">
-        <v>7161511</v>
+        <v>7161610</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4790,10 +4790,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122745523</v>
+        <v>122745527</v>
       </c>
       <c r="B40" t="n">
-        <v>91301</v>
+        <v>74863</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4802,38 +4802,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2062</v>
+        <v>6440</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Nordanbro SV, Vb</t>
+          <t>Nordanbro S, Vb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>776680</v>
+        <v>776667</v>
       </c>
       <c r="R40" t="n">
-        <v>7161613</v>
+        <v>7161621</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4896,10 +4896,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122745525</v>
+        <v>122745519</v>
       </c>
       <c r="B41" t="n">
-        <v>91243</v>
+        <v>98365</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4908,38 +4908,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Nordanbro S, Vb</t>
+          <t>Nordanbro SV, Vb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>776679</v>
+        <v>776678</v>
       </c>
       <c r="R41" t="n">
-        <v>7161607</v>
+        <v>7161562</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5002,10 +5002,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122745515</v>
+        <v>122745516</v>
       </c>
       <c r="B42" t="n">
-        <v>90966</v>
+        <v>98365</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5014,25 +5014,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1204</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5042,10 +5042,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>776765</v>
+        <v>776687</v>
       </c>
       <c r="R42" t="n">
-        <v>7161494</v>
+        <v>7161511</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5108,10 +5108,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122745519</v>
+        <v>122745518</v>
       </c>
       <c r="B43" t="n">
-        <v>98365</v>
+        <v>78798</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5120,25 +5120,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5148,10 +5148,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>776678</v>
+        <v>776674</v>
       </c>
       <c r="R43" t="n">
-        <v>7161562</v>
+        <v>7161575</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5214,10 +5214,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122745522</v>
+        <v>122745517</v>
       </c>
       <c r="B44" t="n">
-        <v>98365</v>
+        <v>90952</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5226,25 +5226,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5254,10 +5254,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>776680</v>
+        <v>776700</v>
       </c>
       <c r="R44" t="n">
-        <v>7161612</v>
+        <v>7161533</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5320,10 +5320,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122745526</v>
+        <v>122745522</v>
       </c>
       <c r="B45" t="n">
-        <v>82553</v>
+        <v>98365</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5332,38 +5332,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Nordanbro S, Vb</t>
+          <t>Nordanbro SV, Vb</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>776671</v>
+        <v>776680</v>
       </c>
       <c r="R45" t="n">
-        <v>7161617</v>
+        <v>7161612</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>

--- a/artfynd/A 14644-2024 artfynd.xlsx
+++ b/artfynd/A 14644-2024 artfynd.xlsx
@@ -4154,7 +4154,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122745521</v>
+        <v>122745522</v>
       </c>
       <c r="B34" t="n">
         <v>98365</v>
@@ -4194,10 +4194,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>776691</v>
+        <v>776680</v>
       </c>
       <c r="R34" t="n">
-        <v>7161596</v>
+        <v>7161612</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4260,10 +4260,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122745515</v>
+        <v>122745517</v>
       </c>
       <c r="B35" t="n">
-        <v>90966</v>
+        <v>90952</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4276,21 +4276,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4300,10 +4300,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>776765</v>
+        <v>776700</v>
       </c>
       <c r="R35" t="n">
-        <v>7161494</v>
+        <v>7161533</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4366,10 +4366,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122745526</v>
+        <v>122745519</v>
       </c>
       <c r="B36" t="n">
-        <v>82553</v>
+        <v>98365</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4378,38 +4378,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Nordanbro S, Vb</t>
+          <t>Nordanbro SV, Vb</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>776671</v>
+        <v>776678</v>
       </c>
       <c r="R36" t="n">
-        <v>7161617</v>
+        <v>7161562</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4472,10 +4472,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122745525</v>
+        <v>122745527</v>
       </c>
       <c r="B37" t="n">
-        <v>91243</v>
+        <v>74863</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4488,21 +4488,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>658</v>
+        <v>6440</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4512,10 +4512,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>776679</v>
+        <v>776667</v>
       </c>
       <c r="R37" t="n">
-        <v>7161607</v>
+        <v>7161621</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4578,10 +4578,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122745523</v>
+        <v>122745515</v>
       </c>
       <c r="B38" t="n">
-        <v>91301</v>
+        <v>90966</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4590,25 +4590,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2062</v>
+        <v>1204</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4618,10 +4618,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>776680</v>
+        <v>776765</v>
       </c>
       <c r="R38" t="n">
-        <v>7161613</v>
+        <v>7161494</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4684,10 +4684,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122745524</v>
+        <v>122745525</v>
       </c>
       <c r="B39" t="n">
-        <v>90952</v>
+        <v>91243</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4700,21 +4700,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4727,7 +4727,7 @@
         <v>776679</v>
       </c>
       <c r="R39" t="n">
-        <v>7161610</v>
+        <v>7161607</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4790,10 +4790,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122745527</v>
+        <v>122745521</v>
       </c>
       <c r="B40" t="n">
-        <v>74863</v>
+        <v>98365</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4802,38 +4802,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Nordanbro S, Vb</t>
+          <t>Nordanbro SV, Vb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>776667</v>
+        <v>776691</v>
       </c>
       <c r="R40" t="n">
-        <v>7161621</v>
+        <v>7161596</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4896,10 +4896,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122745519</v>
+        <v>122745518</v>
       </c>
       <c r="B41" t="n">
-        <v>98365</v>
+        <v>78798</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4908,25 +4908,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4936,10 +4936,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>776678</v>
+        <v>776674</v>
       </c>
       <c r="R41" t="n">
-        <v>7161562</v>
+        <v>7161575</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5002,10 +5002,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122745516</v>
+        <v>122745524</v>
       </c>
       <c r="B42" t="n">
-        <v>98365</v>
+        <v>90952</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5014,38 +5014,38 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Nordanbro SV, Vb</t>
+          <t>Nordanbro S, Vb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>776687</v>
+        <v>776679</v>
       </c>
       <c r="R42" t="n">
-        <v>7161511</v>
+        <v>7161610</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5108,10 +5108,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122745518</v>
+        <v>122745516</v>
       </c>
       <c r="B43" t="n">
-        <v>78798</v>
+        <v>98365</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5120,25 +5120,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5148,10 +5148,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>776674</v>
+        <v>776687</v>
       </c>
       <c r="R43" t="n">
-        <v>7161575</v>
+        <v>7161511</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5214,10 +5214,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122745517</v>
+        <v>122745523</v>
       </c>
       <c r="B44" t="n">
-        <v>90952</v>
+        <v>91301</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5226,25 +5226,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>2062</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5254,10 +5254,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>776700</v>
+        <v>776680</v>
       </c>
       <c r="R44" t="n">
-        <v>7161533</v>
+        <v>7161613</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5320,10 +5320,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122745522</v>
+        <v>122745526</v>
       </c>
       <c r="B45" t="n">
-        <v>98365</v>
+        <v>82553</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5332,38 +5332,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Nordanbro SV, Vb</t>
+          <t>Nordanbro S, Vb</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>776680</v>
+        <v>776671</v>
       </c>
       <c r="R45" t="n">
-        <v>7161612</v>
+        <v>7161617</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>

--- a/artfynd/A 14644-2024 artfynd.xlsx
+++ b/artfynd/A 14644-2024 artfynd.xlsx
@@ -4048,10 +4048,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122745520</v>
+        <v>122745527</v>
       </c>
       <c r="B33" t="n">
-        <v>92233</v>
+        <v>74863</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4060,38 +4060,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4364</v>
+        <v>6440</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Nordanbro SV, Vb</t>
+          <t>Nordanbro S, Vb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>776684</v>
+        <v>776667</v>
       </c>
       <c r="R33" t="n">
-        <v>7161591</v>
+        <v>7161621</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4154,7 +4154,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122745522</v>
+        <v>122745516</v>
       </c>
       <c r="B34" t="n">
         <v>98365</v>
@@ -4194,10 +4194,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>776680</v>
+        <v>776687</v>
       </c>
       <c r="R34" t="n">
-        <v>7161612</v>
+        <v>7161511</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4260,10 +4260,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122745517</v>
+        <v>122745520</v>
       </c>
       <c r="B35" t="n">
-        <v>90952</v>
+        <v>92233</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4272,25 +4272,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4300,10 +4300,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>776700</v>
+        <v>776684</v>
       </c>
       <c r="R35" t="n">
-        <v>7161533</v>
+        <v>7161591</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4366,10 +4366,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122745519</v>
+        <v>122745517</v>
       </c>
       <c r="B36" t="n">
-        <v>98365</v>
+        <v>90952</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4378,25 +4378,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4406,10 +4406,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>776678</v>
+        <v>776700</v>
       </c>
       <c r="R36" t="n">
-        <v>7161562</v>
+        <v>7161533</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4472,10 +4472,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122745527</v>
+        <v>122745524</v>
       </c>
       <c r="B37" t="n">
-        <v>74863</v>
+        <v>90952</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4488,21 +4488,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4512,10 +4512,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>776667</v>
+        <v>776679</v>
       </c>
       <c r="R37" t="n">
-        <v>7161621</v>
+        <v>7161610</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4578,10 +4578,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122745515</v>
+        <v>122745519</v>
       </c>
       <c r="B38" t="n">
-        <v>90966</v>
+        <v>98365</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4590,25 +4590,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1204</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4618,10 +4618,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>776765</v>
+        <v>776678</v>
       </c>
       <c r="R38" t="n">
-        <v>7161494</v>
+        <v>7161562</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4684,10 +4684,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122745525</v>
+        <v>122745521</v>
       </c>
       <c r="B39" t="n">
-        <v>91243</v>
+        <v>98365</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4696,38 +4696,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Nordanbro S, Vb</t>
+          <t>Nordanbro SV, Vb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>776679</v>
+        <v>776691</v>
       </c>
       <c r="R39" t="n">
-        <v>7161607</v>
+        <v>7161596</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4790,10 +4790,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122745521</v>
+        <v>122745523</v>
       </c>
       <c r="B40" t="n">
-        <v>98365</v>
+        <v>91301</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4806,21 +4806,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>2062</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4830,10 +4830,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>776691</v>
+        <v>776680</v>
       </c>
       <c r="R40" t="n">
-        <v>7161596</v>
+        <v>7161613</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4896,10 +4896,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122745518</v>
+        <v>122745525</v>
       </c>
       <c r="B41" t="n">
-        <v>78798</v>
+        <v>91243</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4912,34 +4912,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>185</v>
+        <v>658</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Nordanbro SV, Vb</t>
+          <t>Nordanbro S, Vb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>776674</v>
+        <v>776679</v>
       </c>
       <c r="R41" t="n">
-        <v>7161575</v>
+        <v>7161607</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5002,10 +5002,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122745524</v>
+        <v>122745522</v>
       </c>
       <c r="B42" t="n">
-        <v>90952</v>
+        <v>98365</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5014,38 +5014,38 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Nordanbro S, Vb</t>
+          <t>Nordanbro SV, Vb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>776679</v>
+        <v>776680</v>
       </c>
       <c r="R42" t="n">
-        <v>7161610</v>
+        <v>7161612</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5108,10 +5108,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122745516</v>
+        <v>122745526</v>
       </c>
       <c r="B43" t="n">
-        <v>98365</v>
+        <v>82553</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5120,38 +5120,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Nordanbro SV, Vb</t>
+          <t>Nordanbro S, Vb</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>776687</v>
+        <v>776671</v>
       </c>
       <c r="R43" t="n">
-        <v>7161511</v>
+        <v>7161617</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5214,10 +5214,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122745523</v>
+        <v>122745518</v>
       </c>
       <c r="B44" t="n">
-        <v>91301</v>
+        <v>78798</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5226,25 +5226,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2062</v>
+        <v>185</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5254,10 +5254,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>776680</v>
+        <v>776674</v>
       </c>
       <c r="R44" t="n">
-        <v>7161613</v>
+        <v>7161575</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5320,10 +5320,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122745526</v>
+        <v>122745515</v>
       </c>
       <c r="B45" t="n">
-        <v>82553</v>
+        <v>90966</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5336,34 +5336,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1312</v>
+        <v>1204</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Nordanbro S, Vb</t>
+          <t>Nordanbro SV, Vb</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>776671</v>
+        <v>776765</v>
       </c>
       <c r="R45" t="n">
-        <v>7161617</v>
+        <v>7161494</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>

--- a/artfynd/A 14644-2024 artfynd.xlsx
+++ b/artfynd/A 14644-2024 artfynd.xlsx
@@ -4154,10 +4154,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122745516</v>
+        <v>122745520</v>
       </c>
       <c r="B34" t="n">
-        <v>98365</v>
+        <v>92233</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4166,25 +4166,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4194,10 +4194,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>776687</v>
+        <v>776684</v>
       </c>
       <c r="R34" t="n">
-        <v>7161511</v>
+        <v>7161591</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4260,10 +4260,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122745520</v>
+        <v>122745516</v>
       </c>
       <c r="B35" t="n">
-        <v>92233</v>
+        <v>98365</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4272,25 +4272,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4300,10 +4300,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>776684</v>
+        <v>776687</v>
       </c>
       <c r="R35" t="n">
-        <v>7161591</v>
+        <v>7161511</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>

--- a/artfynd/A 14644-2024 artfynd.xlsx
+++ b/artfynd/A 14644-2024 artfynd.xlsx
@@ -4790,10 +4790,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122745523</v>
+        <v>122745525</v>
       </c>
       <c r="B40" t="n">
-        <v>91301</v>
+        <v>91243</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4802,38 +4802,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2062</v>
+        <v>658</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Nordanbro SV, Vb</t>
+          <t>Nordanbro S, Vb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>776680</v>
+        <v>776679</v>
       </c>
       <c r="R40" t="n">
-        <v>7161613</v>
+        <v>7161607</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4896,10 +4896,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122745525</v>
+        <v>122745523</v>
       </c>
       <c r="B41" t="n">
-        <v>91243</v>
+        <v>91301</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4908,38 +4908,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>658</v>
+        <v>2062</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Nordanbro S, Vb</t>
+          <t>Nordanbro SV, Vb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>776679</v>
+        <v>776680</v>
       </c>
       <c r="R41" t="n">
-        <v>7161607</v>
+        <v>7161613</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>

--- a/artfynd/A 14644-2024 artfynd.xlsx
+++ b/artfynd/A 14644-2024 artfynd.xlsx
@@ -4790,10 +4790,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122745525</v>
+        <v>122745523</v>
       </c>
       <c r="B40" t="n">
-        <v>91243</v>
+        <v>91301</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4802,38 +4802,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>658</v>
+        <v>2062</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Nordanbro S, Vb</t>
+          <t>Nordanbro SV, Vb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>776679</v>
+        <v>776680</v>
       </c>
       <c r="R40" t="n">
-        <v>7161607</v>
+        <v>7161613</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4896,10 +4896,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122745523</v>
+        <v>122745525</v>
       </c>
       <c r="B41" t="n">
-        <v>91301</v>
+        <v>91243</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4908,38 +4908,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2062</v>
+        <v>658</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Nordanbro SV, Vb</t>
+          <t>Nordanbro S, Vb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>776680</v>
+        <v>776679</v>
       </c>
       <c r="R41" t="n">
-        <v>7161613</v>
+        <v>7161607</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>

--- a/artfynd/A 14644-2024 artfynd.xlsx
+++ b/artfynd/A 14644-2024 artfynd.xlsx
@@ -4048,10 +4048,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122745527</v>
+        <v>122745516</v>
       </c>
       <c r="B33" t="n">
-        <v>74863</v>
+        <v>98368</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4060,38 +4060,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Nordanbro S, Vb</t>
+          <t>Nordanbro SV, Vb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>776667</v>
+        <v>776687</v>
       </c>
       <c r="R33" t="n">
-        <v>7161621</v>
+        <v>7161511</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4154,10 +4154,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122745520</v>
+        <v>122745523</v>
       </c>
       <c r="B34" t="n">
-        <v>92233</v>
+        <v>91304</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4166,25 +4166,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4364</v>
+        <v>2062</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4194,10 +4194,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>776684</v>
+        <v>776680</v>
       </c>
       <c r="R34" t="n">
-        <v>7161591</v>
+        <v>7161613</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4260,10 +4260,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122745516</v>
+        <v>122745524</v>
       </c>
       <c r="B35" t="n">
-        <v>98365</v>
+        <v>90955</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4272,38 +4272,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Nordanbro SV, Vb</t>
+          <t>Nordanbro S, Vb</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>776687</v>
+        <v>776679</v>
       </c>
       <c r="R35" t="n">
-        <v>7161511</v>
+        <v>7161610</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4366,10 +4366,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122745517</v>
+        <v>122745526</v>
       </c>
       <c r="B36" t="n">
-        <v>90952</v>
+        <v>82556</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4382,34 +4382,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Nordanbro SV, Vb</t>
+          <t>Nordanbro S, Vb</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>776700</v>
+        <v>776671</v>
       </c>
       <c r="R36" t="n">
-        <v>7161533</v>
+        <v>7161617</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4472,10 +4472,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122745524</v>
+        <v>122745525</v>
       </c>
       <c r="B37" t="n">
-        <v>90952</v>
+        <v>91242</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4488,21 +4488,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4515,7 +4515,7 @@
         <v>776679</v>
       </c>
       <c r="R37" t="n">
-        <v>7161610</v>
+        <v>7161607</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4578,10 +4578,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122745519</v>
+        <v>122745517</v>
       </c>
       <c r="B38" t="n">
-        <v>98365</v>
+        <v>90955</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4590,25 +4590,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4618,10 +4618,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>776678</v>
+        <v>776700</v>
       </c>
       <c r="R38" t="n">
-        <v>7161562</v>
+        <v>7161533</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4684,10 +4684,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122745521</v>
+        <v>122745519</v>
       </c>
       <c r="B39" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4724,10 +4724,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>776691</v>
+        <v>776678</v>
       </c>
       <c r="R39" t="n">
-        <v>7161596</v>
+        <v>7161562</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4790,10 +4790,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122745523</v>
+        <v>122745515</v>
       </c>
       <c r="B40" t="n">
-        <v>91301</v>
+        <v>90969</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4802,25 +4802,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2062</v>
+        <v>1204</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4830,10 +4830,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>776680</v>
+        <v>776765</v>
       </c>
       <c r="R40" t="n">
-        <v>7161613</v>
+        <v>7161494</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4896,10 +4896,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122745525</v>
+        <v>122745527</v>
       </c>
       <c r="B41" t="n">
-        <v>91243</v>
+        <v>74866</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4912,21 +4912,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>658</v>
+        <v>6440</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4936,10 +4936,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>776679</v>
+        <v>776667</v>
       </c>
       <c r="R41" t="n">
-        <v>7161607</v>
+        <v>7161621</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5002,10 +5002,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122745522</v>
+        <v>122745521</v>
       </c>
       <c r="B42" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5042,10 +5042,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>776680</v>
+        <v>776691</v>
       </c>
       <c r="R42" t="n">
-        <v>7161612</v>
+        <v>7161596</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5108,10 +5108,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122745526</v>
+        <v>122745518</v>
       </c>
       <c r="B43" t="n">
-        <v>82553</v>
+        <v>78801</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5124,34 +5124,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1312</v>
+        <v>185</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Nordanbro S, Vb</t>
+          <t>Nordanbro SV, Vb</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>776671</v>
+        <v>776674</v>
       </c>
       <c r="R43" t="n">
-        <v>7161617</v>
+        <v>7161575</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5214,10 +5214,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122745518</v>
+        <v>122745520</v>
       </c>
       <c r="B44" t="n">
-        <v>78798</v>
+        <v>92236</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5226,25 +5226,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>185</v>
+        <v>4364</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5254,10 +5254,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>776674</v>
+        <v>776684</v>
       </c>
       <c r="R44" t="n">
-        <v>7161575</v>
+        <v>7161591</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5320,10 +5320,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122745515</v>
+        <v>122745522</v>
       </c>
       <c r="B45" t="n">
-        <v>90966</v>
+        <v>98368</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5332,25 +5332,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1204</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5360,10 +5360,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>776765</v>
+        <v>776680</v>
       </c>
       <c r="R45" t="n">
-        <v>7161494</v>
+        <v>7161612</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>

--- a/artfynd/A 14644-2024 artfynd.xlsx
+++ b/artfynd/A 14644-2024 artfynd.xlsx
@@ -4048,10 +4048,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122745516</v>
+        <v>122745525</v>
       </c>
       <c r="B33" t="n">
-        <v>98368</v>
+        <v>91244</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4060,38 +4060,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Nordanbro SV, Vb</t>
+          <t>Nordanbro S, Vb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>776687</v>
+        <v>776679</v>
       </c>
       <c r="R33" t="n">
-        <v>7161511</v>
+        <v>7161607</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4154,10 +4154,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122745523</v>
+        <v>122745517</v>
       </c>
       <c r="B34" t="n">
-        <v>91304</v>
+        <v>90957</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4166,25 +4166,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2062</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4194,10 +4194,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>776680</v>
+        <v>776700</v>
       </c>
       <c r="R34" t="n">
-        <v>7161613</v>
+        <v>7161533</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4260,10 +4260,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122745524</v>
+        <v>122745523</v>
       </c>
       <c r="B35" t="n">
-        <v>90955</v>
+        <v>91306</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4272,38 +4272,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>2062</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Nordanbro S, Vb</t>
+          <t>Nordanbro SV, Vb</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>776679</v>
+        <v>776680</v>
       </c>
       <c r="R35" t="n">
-        <v>7161610</v>
+        <v>7161613</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4366,10 +4366,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122745526</v>
+        <v>122745520</v>
       </c>
       <c r="B36" t="n">
-        <v>82556</v>
+        <v>92238</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4378,38 +4378,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1312</v>
+        <v>4364</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Nordanbro S, Vb</t>
+          <t>Nordanbro SV, Vb</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>776671</v>
+        <v>776684</v>
       </c>
       <c r="R36" t="n">
-        <v>7161617</v>
+        <v>7161591</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4472,10 +4472,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122745525</v>
+        <v>122745515</v>
       </c>
       <c r="B37" t="n">
-        <v>91242</v>
+        <v>90971</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4488,34 +4488,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>658</v>
+        <v>1204</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Nordanbro S, Vb</t>
+          <t>Nordanbro SV, Vb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>776679</v>
+        <v>776765</v>
       </c>
       <c r="R37" t="n">
-        <v>7161607</v>
+        <v>7161494</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4578,10 +4578,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122745517</v>
+        <v>122745519</v>
       </c>
       <c r="B38" t="n">
-        <v>90955</v>
+        <v>98370</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4590,25 +4590,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4618,10 +4618,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>776700</v>
+        <v>776678</v>
       </c>
       <c r="R38" t="n">
-        <v>7161533</v>
+        <v>7161562</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4684,10 +4684,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122745519</v>
+        <v>122745522</v>
       </c>
       <c r="B39" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4724,10 +4724,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>776678</v>
+        <v>776680</v>
       </c>
       <c r="R39" t="n">
-        <v>7161562</v>
+        <v>7161612</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4790,10 +4790,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122745515</v>
+        <v>122745521</v>
       </c>
       <c r="B40" t="n">
-        <v>90969</v>
+        <v>98370</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4802,25 +4802,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1204</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4830,10 +4830,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>776765</v>
+        <v>776691</v>
       </c>
       <c r="R40" t="n">
-        <v>7161494</v>
+        <v>7161596</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5002,10 +5002,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122745521</v>
+        <v>122745526</v>
       </c>
       <c r="B42" t="n">
-        <v>98368</v>
+        <v>82558</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5014,38 +5014,38 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Nordanbro SV, Vb</t>
+          <t>Nordanbro S, Vb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>776691</v>
+        <v>776671</v>
       </c>
       <c r="R42" t="n">
-        <v>7161596</v>
+        <v>7161617</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5111,7 +5111,7 @@
         <v>122745518</v>
       </c>
       <c r="B43" t="n">
-        <v>78801</v>
+        <v>78803</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5214,10 +5214,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122745520</v>
+        <v>122745516</v>
       </c>
       <c r="B44" t="n">
-        <v>92236</v>
+        <v>98370</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5226,25 +5226,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5254,10 +5254,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>776684</v>
+        <v>776687</v>
       </c>
       <c r="R44" t="n">
-        <v>7161591</v>
+        <v>7161511</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5320,10 +5320,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122745522</v>
+        <v>122745524</v>
       </c>
       <c r="B45" t="n">
-        <v>98368</v>
+        <v>90957</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5332,38 +5332,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Nordanbro SV, Vb</t>
+          <t>Nordanbro S, Vb</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>776680</v>
+        <v>776679</v>
       </c>
       <c r="R45" t="n">
-        <v>7161612</v>
+        <v>7161610</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>

--- a/artfynd/A 14644-2024 artfynd.xlsx
+++ b/artfynd/A 14644-2024 artfynd.xlsx
@@ -4260,10 +4260,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122745523</v>
+        <v>122745515</v>
       </c>
       <c r="B35" t="n">
-        <v>91306</v>
+        <v>90971</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4272,25 +4272,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2062</v>
+        <v>1204</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4300,10 +4300,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>776680</v>
+        <v>776765</v>
       </c>
       <c r="R35" t="n">
-        <v>7161613</v>
+        <v>7161494</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4472,10 +4472,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122745515</v>
+        <v>122745523</v>
       </c>
       <c r="B37" t="n">
-        <v>90971</v>
+        <v>91306</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4484,25 +4484,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1204</v>
+        <v>2062</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4512,10 +4512,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>776765</v>
+        <v>776680</v>
       </c>
       <c r="R37" t="n">
-        <v>7161494</v>
+        <v>7161613</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5108,10 +5108,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122745518</v>
+        <v>122745516</v>
       </c>
       <c r="B43" t="n">
-        <v>78803</v>
+        <v>98370</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5120,25 +5120,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5148,10 +5148,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>776674</v>
+        <v>776687</v>
       </c>
       <c r="R43" t="n">
-        <v>7161575</v>
+        <v>7161511</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5214,10 +5214,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122745516</v>
+        <v>122745518</v>
       </c>
       <c r="B44" t="n">
-        <v>98370</v>
+        <v>78803</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5226,25 +5226,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5254,10 +5254,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>776687</v>
+        <v>776674</v>
       </c>
       <c r="R44" t="n">
-        <v>7161511</v>
+        <v>7161575</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
